--- a/Employee_Reports_wi52/Wycliffe Mushori Q0592.xlsx
+++ b/Employee_Reports_wi52/Wycliffe Mushori Q0592.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1203,11 +1203,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1351,11 +1351,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1388,11 +1388,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1437,11 +1437,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1584,11 +1584,11 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1621,11 +1621,11 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1658,11 +1658,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1695,11 +1695,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1744,11 +1744,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1793,11 +1793,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1830,11 +1830,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1879,11 +1879,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1907,20 +1907,20 @@
       <c r="E32" s="3" t="inlineStr"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2025</t>
+          <t>26-Aug-2026</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2027</t>
+          <t>25-Aug-2028</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>315</v>
+        <v>728</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
